--- a/sources/armorking_step6b.xlsx
+++ b/sources/armorking_step6b.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">

--- a/sources/armorking_step6b.xlsx
+++ b/sources/armorking_step6b.xlsx
@@ -1102,6 +1102,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
@@ -1139,6 +1144,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>da3a1275-cb0c-4106-8641-cfa9ccdf3ec7</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>da3a1275-cb0c-4106-8641-cfa9ccdf3ec7</t>
@@ -1181,6 +1191,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>c59ded73-4975-409c-9fcb-97f64f823e1f</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>c59ded73-4975-409c-9fcb-97f64f823e1f</t>
@@ -1223,6 +1238,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>4bfbb956-22f3-4aa3-8b36-b331246b3633</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>4bfbb956-22f3-4aa3-8b36-b331246b3633</t>
@@ -1265,6 +1285,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>b017afe8-35fe-4676-b2eb-d81bccc55df5</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>b017afe8-35fe-4676-b2eb-d81bccc55df5</t>
@@ -1317,6 +1342,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>4032df9b-cac0-4300-a750-9f6328f0125c</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>4032df9b-cac0-4300-a750-9f6328f0125c</t>
@@ -1364,6 +1394,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>03ae734c-c034-4a04-8b1f-1969120d9045</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
           <t>03ae734c-c034-4a04-8b1f-1969120d9045</t>
@@ -1409,6 +1444,11 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>f38eafdb-7ad2-4d22-a656-ee63cb402a1e</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -5489,6 +5529,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
+        </is>
+      </c>
       <c r="R96" t="inlineStr">
         <is>
           <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
@@ -5526,6 +5571,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>ab4325ea-0934-4517-856d-7640da4c01f7</t>
+        </is>
+      </c>
       <c r="R97" t="inlineStr">
         <is>
           <t>ab4325ea-0934-4517-856d-7640da4c01f7</t>
@@ -5568,6 +5618,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
+        </is>
+      </c>
       <c r="R98" t="inlineStr">
         <is>
           <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
@@ -5610,6 +5665,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>fc691ddf-15db-4695-a8e9-7430fe664066</t>
+        </is>
+      </c>
       <c r="R99" t="inlineStr">
         <is>
           <t>fc691ddf-15db-4695-a8e9-7430fe664066</t>
@@ -5650,6 +5710,11 @@
       <c r="M100" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>fdcf2a53-d956-49ec-97b6-76739cea2462</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -5799,6 +5864,11 @@
           <t>hhmmhLLLmm</t>
         </is>
       </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>21571b37-4525-4b34-9433-0797a86f473f</t>
+        </is>
+      </c>
       <c r="R104" t="inlineStr">
         <is>
           <t>21571b37-4525-4b34-9433-0797a86f473f</t>
@@ -5829,6 +5899,11 @@
       <c r="K105" t="inlineStr">
         <is>
           <t>hmmhLLLmm</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>3d0c8edd-a764-4366-833c-c7fe06fc9cc8</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">

--- a/sources/armorking_step6b.xlsx
+++ b/sources/armorking_step6b.xlsx
@@ -1124,6 +1124,11 @@
           <t>– 1,2,1,2,1</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1,2,1,1,2</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>– Ultimate Punches</t>
@@ -1169,6 +1174,11 @@
       <c r="A15" t="inlineStr">
         <is>
           <t>– 2,1,2,2,1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2,1,2,1,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
